--- a/docs/TBookStore_MasterPlan.xlsx
+++ b/docs/TBookStore_MasterPlan.xlsx
@@ -56,7 +56,7 @@
     <t xml:space="preserve">Kiến trúc</t>
   </si>
   <si>
-    <t xml:space="preserve">Khởi tạo project .NET 8 Web API, cấu trúc layer Controller/Service/Repository</t>
+    <t xml:space="preserve">Khởi tạo project FastAPI (Python 3.12), cấu trúc layer Router/Service/Repository</t>
   </si>
   <si>
     <t xml:space="preserve">Must</t>
@@ -77,7 +77,7 @@
     <t xml:space="preserve">Database</t>
   </si>
   <si>
-    <t xml:space="preserve">Chuyển schema MySQL → SQL Server (kiểu dữ liệu, ENUM→CHECK, AUTO_INCREMENT→IDENTITY)</t>
+    <t xml:space="preserve">Chuyển schema MySQL → PostgreSQL (kiểu dữ liệu, giữ ENUM type, AUTO_INCREMENT→GENERATED ALWAYS AS IDENTITY)</t>
   </si>
   <si>
     <t xml:space="preserve">1d</t>
@@ -89,7 +89,7 @@
     <t xml:space="preserve">Giữ nguyên tên bảng/cột để đỡ phải đổi logic nghiệp vụ</t>
   </si>
   <si>
-    <t xml:space="preserve">Cấu hình Dapper + connection factory + stored procedure mẫu</t>
+    <t xml:space="preserve">Cấu hình psycopg 3 + connection pool + stored procedure mẫu</t>
   </si>
   <si>
     <t xml:space="preserve">Auth</t>
@@ -140,7 +140,7 @@
     <t xml:space="preserve">Swagger/OpenAPI setup</t>
   </si>
   <si>
-    <t xml:space="preserve">Docker Compose khung sườn (api + sqlserver)</t>
+    <t xml:space="preserve">Docker Compose khung sườn (api + postgres)</t>
   </si>
   <si>
     <t xml:space="preserve">Should</t>
@@ -296,7 +296,7 @@
     <t xml:space="preserve">Xuất file</t>
   </si>
   <si>
-    <t xml:space="preserve">Xuất PDF hóa đơn/báo cáo bằng QuestPDF</t>
+    <t xml:space="preserve">Xuất PDF hóa đơn/báo cáo bằng ReportLab</t>
   </si>
   <si>
     <t xml:space="preserve">views/*/print.ejs</t>
@@ -308,7 +308,7 @@
     <t xml:space="preserve">Job nền</t>
   </si>
   <si>
-    <t xml:space="preserve">Hàng đợi tác vụ (Hangfire) cho gửi mail &amp; xuất báo cáo lớn</t>
+    <t xml:space="preserve">Hàng đợi tác vụ (Celery) cho gửi mail &amp; xuất báo cáo lớn</t>
   </si>
   <si>
     <t xml:space="preserve">Chất lượng</t>
@@ -329,7 +329,7 @@
     <t xml:space="preserve">middlewares/rateLimit.middleware.js</t>
   </si>
   <si>
-    <t xml:space="preserve">Health check endpoint + logging có cấu trúc (Serilog)</t>
+    <t xml:space="preserve">Health check endpoint + logging có cấu trúc (structlog)</t>
   </si>
   <si>
     <t xml:space="preserve">Triển khai</t>
@@ -401,7 +401,7 @@
     <t xml:space="preserve">Stack</t>
   </si>
   <si>
-    <t xml:space="preserve">.NET 8 (ASP.NET Core) + Dapper + SQL Server + AngularJS + Redis + Docker Compose</t>
+    <t xml:space="preserve">FastAPI (Python 3.12) + psycopg 3 + PostgreSQL + AngularJS + Redis + Docker Compose</t>
   </si>
   <si>
     <t xml:space="preserve">Tham khảo</t>
